--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0050.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0050.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Discord Reverberation</t>
+          <t>Dư Âm Tacet Discord</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Gravity Stream 30m</t>
+          <t>Dòng Trọng Lực 30m</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Dried Fern Spore</t>
+          <t>Bào Tử Dương Xỉ Khô</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Carapace: Automobile</t>
+          <t>Vỏ Giáp: Xe cơ giới</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Cruisewing Finish Circle</t>
+          <t>Vòng Hoàn Kết Cánh Tàu</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Midnight Ranger canh gác</t>
+          <t>Kỵ Sĩ Bóng Đêm Canh Gác</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Novice Gladiator</t>
+          <t>Đấu Sĩ Tân Thủ</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Little Chiani</t>
+          <t>Chiani Nhỏ</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Echo Challenge: Illusion</t>
+          <t>Thử Thách Tiếng Vọng: Ảo Ảnh</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Phải</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Shuncai</t>
+          <t>Thuận Tài</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Kẻ bị ruồng bỏ "Thủ lĩnh"</t>
+          <t>"Thủ lĩnh" bị ruồng bỏ</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Wall of Silence</t>
+          <t>Bức Tường Câm Lặng</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Honeysuckle</t>
+          <t>Kim Ngân Hoa</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Cửa nhà hát</t>
+          <t>Cửa Nhà hát</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Anonymizer</t>
+          <t>Bộ ẩn danh hóa</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Bia mộ mang hương vị đại dương</t>
+          <t>Ngôi mộ mang hơi thở của đại dương</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Xiaomo</t>
+          <t>Tiểu Mặc</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Cửa ra vào Haven of Sprouts</t>
+          <t>Cửa Vào Mầm Xanh Thịnh Vượng</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>KU-HeeHee</t>
+          <t>KU-Hihi</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Shuli</t>
+          <t>Thư Ly</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Cooking Pot</t>
+          <t>Nồi Nấu Ăn</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Người phụ nữ trầm tư</t>
+          <t>Người Phụ Nữ Trầm Ngâm</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Leap of Glory</t>
+          <t>Bước Nhảy Vinh Quang</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Jinfang</t>
+          <t>Kim Phương</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Reverberations of Nimbus Sanctum</t>
+          <t>Dư Âm Của Nimbus Sanctum</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Lính lười biếng</t>
+          <t>Lính Lười</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Floating Container</t>
+          <t>Thùng Chứa Nổi</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Drum</t>
+          <t>Trống</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Spearback King</t>
+          <t>Vua Lưng Lao</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Aurora Kronaclaw</t>
+          <t>Móng Vuốt Krona Băng Giá</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Silver-Banded Lizard</t>
+          <t>Thằn Lằn Vằn Bạc</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Beigu</t>
+          <t>Bắc Cổ</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>: "Heartless Tinman"</t>
+          <t>: "Người Thiếc Vô Tâm"</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Automatic Door</t>
+          <t>Cửa Tự Động</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Acorn</t>
+          <t>Hạt Dẻ</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Regretful Outcast</t>
+          <t>Kẻ Bị Đào Thải Đầy Hối Tiếc</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Hao'bai</t>
+          <t>Hạo Bạch</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Calcified Junrock</t>
+          <t>Đá Junrock Hóa Thạch</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Huilang</t>
+          <t>Hồi Lang</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>"Descend"</t>
+          <t>Hạ xuống</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Bloom Bearer's Illusion</t>
+          <t>Ảo Ảnh Người Mang Hoa</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Fishing Dock</t>
+          <t>Bến Câu Cá</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Yonglu</t>
+          <t>Dũng Lộ</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Flare Crest 3</t>
+          <t>Huy Hiệu Lửa Cấp 3</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Zhenhong</t>
+          <t>Chân Hồng</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Token</t>
+          <t>Mã Đổi</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Quản lý lịch trình</t>
+          <t>Trình quản lý lịch trình</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Trưởng lão cam chịu</t>
+          <t>Trưởng Lão Thất Vọng</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Third Floor</t>
+          <t>Tầng Ba</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Shengying</t>
+          <t>Thăng Anh</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Challenge: Thăng Tiến Pha I</t>
+          <t>Thử Thách: Thăng Hoa Giai Đoạn I</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Bản ghi trạng thái đá chặn cửa Safe House</t>
+          <t>Bản Ghi Trạng Thái Đá Chặn Cửa Nhà An Toàn</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Flamaxis</t>
+          <t>Lửa Hừng</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Cosmos</t>
+          <t>Vũ Trụ</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Eye of Ignorance</t>
+          <t>: Con Mắt Của Vô Minh</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Xem trang nhật ký bí ẩn</t>
+          <t>Xem trang nhật ký bí ẩn.</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Qianling</t>
+          <t>Kiền Lĩnh</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>The Corrupted Core</t>
+          <t>Lõi Bị Nhiễm Độc</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Sit</t>
+          <t>Ngồi đi</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Phantom: Nimbus Wraith</t>
+          <t>Hồn Ma: Bóng Ma Mây Đen</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Enter</t>
+          <t>Vào</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Xem Thông tin</t>
+          <t>Xem Thông Tin</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Greet</t>
+          <t>Xin chào.</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Công dân hào hứng</t>
+          <t>Thật không thể tin được!</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Lên Hạng Cao Hơn</t>
+          <t>Lên Tầng Thượng</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Main Core</t>
+          <t>Lõi Chính</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Kiểm Tra Các Chai Lọ</t>
+          <t>Kiểm tra những chiếc chai lọ</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Optimistic Gladiator</t>
+          <t>Dũng Sĩ Lạc Quan</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Tham Gia "Thử Thách Rèn Luyện"</t>
+          <t>Tham gia "Thử Thách Giả Mạo"</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Pattern Controller</t>
+          <t>Điều Khiển Mẫu</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Người Lính Bất Mãn</t>
+          <t>Lính Bực Mình</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Brant Cube</t>
+          <t>Khối Brant</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Young Dreadmane: Wind</t>
+          <t>Dreadmane Trẻ: Gió</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Bia Mộ Có Quả Viscum Berry</t>
+          <t>Ngôi mộ với trái Viscum Berry</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Xieyang</t>
+          <t>Tạ Dương</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Gravity Box</t>
+          <t>Hộp Trọng Lực</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Uncle Qin</t>
+          <t>Chú Tần</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Thương Nhân Royan Sắc Sảo</t>
+          <t>Thương nhân Royan tinh ranh</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Chặt Đứt Tòa Tháp Bằng Kiếm</t>
+          <t>Chém đứt ngọn tháp bằng thanh kiếm của ngươi</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Fenrico: Sự Giải Cứu Trong Vực Sâu</t>
+          <t>Fenrico: Sự Giải Thoát Trong Sâu Thẳm</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Jianye</t>
+          <t>Kiến Diệp</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Depressed Pilgrim</t>
+          <t>Lữ khách mỏi mệt</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Mountaineer</t>
+          <t>Nhà leo núi</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Shee</t>
+          <t>Shee...</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Nấu ăn</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Cosmos</t>
+          <t>Vũ Trụ</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Voidspawn: Mining Drone</t>
+          <t>Voidspawn: Drone Khai Thác</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Do</t>
+          <t>Làm</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Đuổi theo Phrolova</t>
+          <t>Truy đuổi Phrolova</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Cấp Độ Vinh Quang Đề Xuất: 301-400</t>
+          <t>Cấp Vinh Quang đề xuất: 301-400</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Cluster Prism · Fusion</t>
+          <t>Lăng Kính Cụm · Fusion</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Changli's Phantom</t>
+          <t>Ảo ảnh của Changli</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Học Sinh Chán Nản</t>
+          <t>Học sinh chán đời</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Worried Midnight Ranger</t>
+          <t>Midnight Ranger Lo Âu</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Foss</t>
+          <t>Hóa thạch</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Hearthbear</t>
+          <t>Gấu Lửa Ấm</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Mysterious Black Cat</t>
+          <t>Mèo Đen Bí Ẩn</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Davide's Voyage Log</t>
+          <t>Nhật Ký Hành Trình của Davide</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Reassured Gladiator</t>
+          <t>Đấu Sĩ An Tâm</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Rương Cung Cấp Cao Cấp</t>
+          <t>Premium Supply Chest</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Construct: Protective Scales</t>
+          <t>Cấu Trúc: Vảy Bảo Hộ</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Nhật ký Bị Loại II</t>
+          <t>Nhật Ký Bị Loại II</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Voidspawn: Sabercat Prowler</t>
+          <t>Voidspawn: Mãnh Hổ Tuần Dã</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>: "Aunt Em"</t>
+          <t>: "Dì Em"</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Lấy Tần Số</t>
+          <t>Thu thập tần số</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Jellyfish Area</t>
+          <t>Khu Vực Sứa</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Yêu Cầu Cô Gái Đứng Lên Thiết Bị</t>
+          <t>Bảo cô bé đứng lên thiết bị</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Thundering Mephis: Lightening Fury</t>
+          <t>Mephis Sấm Sét: Cơn Thịnh Nộ Sấm Sét</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Sự Kiện Đã Kết Thúc</t>
+          <t>Sự kiện này đã kết thúc</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Logistics</t>
+          <t>Hậu Cần</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Nhóm Giám Sát Thang Máy</t>
+          <t>Nhóm màn hình thang máy</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Lotus Seeds</t>
+          <t>Hạt Sen</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Soul Stone</t>
+          <t>Viên Linh Hồn</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Leaftail Fox</t>
+          <t>Cáo Đuôi Lá</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14854,7 +14854,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Học Sinh Luyến Lưu</t>
+          <t>Học Sinh Lưu Luyến</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Inspect</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14994,7 +14994,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Cloudy</t>
+          <t>U Ám</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Up</t>
+          <t>Vút Lên</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15554,7 +15554,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Blazing Cutlass</t>
+          <t>Dao Lửa Blaze</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Clock</t>
+          <t>Đồng hồ</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Nhân Viên Văn Phòng Trầm Cảm</t>
+          <t>Nhân viên văn phòng chán chường</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Initiate</t>
+          <t>Bắt đầu</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Bình Tưới Nước</t>
+          <t>Bình tưới nước</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Damaged Report</t>
+          <t>Báo Cáo Hư Hỏng</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Bắt Đầu Giao Hàng</t>
+          <t>Bắt đầu giao hàng</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Xiuyi</t>
+          <t>Tú Nghị</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17024,7 +17024,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Doll</t>
+          <t>Búp bê</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Redbell</t>
+          <t>Hoa chuông đỏ</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Lính Canh Nhà Tắm</t>
+          <t>Vệ Binh Nhà Tắm</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Crow</t>
+          <t>Quạ</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Nhận Lời Mời Từ Kiến Trúc Sư Vĩ Đại</t>
+          <t>Nhận lời mời của Kiến Trúc Sư Vĩ Đại</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Tidal Supply Chest</t>
+          <t>Rương Cung cấp Thủy Triều</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Mutant Organism: Geohide Saurian Large</t>
+          <t>Sinh vật thể đột biến: Geohide Saurian Large</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Tower Predator</t>
+          <t>Kẻ Săn Mồi Trong Tháp</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Perplexed Noble</t>
+          <t>Quý Tộc Bối Rối</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Hoochief: Thường: Wind</t>
+          <t>Thủ Lĩnh Hoo: Thường - Gió</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Dissatisfied Priestess</t>
+          <t>Tư Tế Bất Mãn</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Inspect</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Kiểm Tra Các Dòng Chữ</t>
+          <t>Kiểm tra những dòng chữ khắc</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Điểm Câu Cá Được Tạo Bởi Mồi Cát Giun</t>
+          <t>Điểm Câu Tạo Bởi Mồi Giun Cát</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Đi Tuần Tra</t>
+          <t>Đi tuần tra đi</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Chat</t>
+          <t>Trò Chuyện</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Giấc Mơ Tuyệt Vọng</t>
+          <t>: Giấc Mơ Tuyệt Vọng</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>About Rongqing</t>
+          <t>Về Rongqing</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Lắng Nghe Những Ảo Ảnh</t>
+          <t>Hãy lắng nghe những ảo ảnh</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Mingjing</t>
+          <t>Minh Tĩnh</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19894,7 +19894,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Still Infatuated Samara</t>
+          <t>Samara Vẫn Còn Say Đắm</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19964,7 +19964,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Competent Pioneer Association Photographer</t>
+          <t>Nhiếp Ảnh Gia Hiệp Hội Tiên Phong Đầy Năng Lực</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Đi Sạc Năng Lượng</t>
+          <t>Tiến lên và sạc năng lượng đi</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Hồi Tưởng Lại Thời Điểm Viện Nghiên Cứu Lâm Vào Khủng Hoảng</t>
+          <t>Hồi tưởng lại thời khắc Viện Nghiên Cứu lâm nguy</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Sad Lottie Lost</t>
+          <t>Lottie Đau Buồn Vì Lạc Lối</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Garga Goose</t>
+          <t>Ngỗng Garga</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Panoram</t>
+          <t>Toàn cảnh</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>: Aberrant Nightmare</t>
+          <t>: Ác Mộng Quái Dị</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Troupe Liner</t>
+          <t>Thành Viên Đoàn Xiếc</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Điều Tra Chiếc Hộp</t>
+          <t>Kiểm tra cái hộp này</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Lost Info Tablet</t>
+          <t>Mảnh Bảng Thông Tin Lạc Mất</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Changshui</t>
+          <t>Trường Thủy</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Gõ Cửa Sổ</t>
+          <t>Gõ vào cửa sổ</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Wuli</t>
+          <t>Vô Lợi</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Giáo</t>
+          <t>Nhà Nghiên Cứu Lao</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Aria Mummer</t>
+          <t>Diễn Viên Aria</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Dâng Lòng Trung Thành</t>
+          <t>Thề trung thành</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Lunarum Bough</t>
+          <t>Cành Lunarum</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21924,7 +21924,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Hidden Platform</t>
+          <t>Nền Tảng Ẩn</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Hoverdroid: Shooter</t>
+          <t>Robot Bay Lượn: Bộ phận bắn</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Deliver Soliseeds</t>
+          <t>Giao Hạt Soliseed</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22204,7 +22204,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Domain Entrance_Temporary</t>
+          <t>Lối Vào Tổ Tacet_Tạm Thời</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Rider Weapon</t>
+          <t>Vũ Khí Kỵ Sĩ</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22344,7 +22344,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Investigate</t>
+          <t>Điều Tra</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Kronaclaw</t>
+          <t>Móng Vuốt Hắc Ám</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Injured Passerby</t>
+          <t>Người qua đường bị thương</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Dingchun</t>
+          <t>Đinh Xuân</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>: Fading Ultramarine</t>
+          <t>: Lam Tàn Phai</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22974,7 +22974,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Trưởng Lão Yếu Ớt</t>
+          <t>Trưởng Lão yếu đuối</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Xoay Theo Chiều Kim Đồng Hồ 90°</t>
+          <t>Xoay 90° theo chiều kim đồng hồ</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Kiểm Tra Tảng Đá</t>
+          <t>Kiểm tra tảng đá kia</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23464,7 +23464,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Bản Sao Aalto</t>
+          <t>Bản sao của Aalto</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23604,7 +23604,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Rời Khỏi Twilight Rise</t>
+          <t>Rời khỏi Twilight Rise đi</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Nói Chuyện Với Cô Gái Royan</t>
+          <t>Nói chuyện với cô gái Roya</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Voidspawn: Spacetrek Explorer</t>
+          <t>Voidspawn: Nhà Thám Hiểm Không Gian</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Sequence Mechanism</t>
+          <t>Cơ Chế Trình Tự</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Vào sảnh giao dịch</t>
+          <t>Bước vào sảnh giao dịch</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24094,8 +24094,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Yi’an
-```</t>
+          <t>Yi’an</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -24165,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Nhặt tia sáng</t>
+          <t>Nhặt tia sáng le lói</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24235,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Gemma</t>
+          <t>Ngọc Gemma</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24305,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Pilgrim's Shell</t>
+          <t>Vỏ Sò Hành Hương</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24375,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Nocturnus Knight</t>
+          <t>Hiệp Sĩ Nocturnus</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24515,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Grandma Jue</t>
+          <t>Bà Jue</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24585,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Xiaomu</t>
+          <t>Tiểu Mộc</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24655,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Coral Oats</t>
+          <t>Yến Mạch San Hô</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24725,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Nhặt</t>
+          <t>Nhặt Lên</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24865,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Weiqi Bowl</t>
+          <t>Bát cờ Vây</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24935,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Quý Cô Biển Cả</t>
+          <t>Nữ Thần Biển Cả</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25005,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Nightmare: Thundering Mephis</t>
+          <t>Ác Mộng: Thundering Mephis</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25075,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>"Occupied Body"</t>
+          <t>"Thân Xác Bị Chiếm Đoạt"</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25145,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Camellya Cube</t>
+          <t>Khối Camellya</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25285,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Bước vào Resounding Rise</t>
+          <t>Bước vào Resounding Rise.</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25355,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Fire Wind Shot</t>
+          <t>Bắn Cầu Gió Lửa</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25425,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Bước vào khán phòng</t>
+          <t>Vào khán phòng</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25565,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Elite Dreadmane: Fusion</t>
+          <t>Dreadmane Cấp Tinh Anh: Fusion</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25705,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Bộ Áp Dụng Sơn</t>
+          <t>Bộ áp họa tiết</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25775,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Gợi ý một bộ phim hành động</t>
+          <t>Gợi ý một bộ phim hành động đi</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -26265,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Để lại một quả nón Creeping Torchpine</t>
+          <t>Bỏ lại một quả nón Thông Lửa Leo</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26335,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Angry Shepherd</t>
+          <t>Người Chăn Cừu Giận Dữ</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26615,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Ký ức Vết Nhơ</t>
+          <t>Ký Ức Vết Nhơ</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26685,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26965,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Nghiên cứu Records</t>
+          <t>Hồ sơ Nghiên cứu</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27035,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Enter Tidal Defense Simulator</t>
+          <t>Bước vào Mô Phỏng Phòng Thủ Thủy Triều</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27105,7 +27104,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Nói chuyện lại</t>
+          <t>Nói tiếp đi</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27175,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Male Bloom Bearer</t>
+          <t>Nam - Người Mang Hoa Nở</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27385,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Công dân Chu đáo</t>
+          <t>Công Dân Chu Đáo</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27455,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Knipper</t>
+          <t>Gõ Cửa</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27595,7 +27594,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Blinking Soliskin Collection Point</t>
+          <t>Điểm Thu Thập Da Soliskin Nhấp Nháy</t>
         </is>
       </c>
       <c r="N388" t="inlineStr">
@@ -27735,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Basic Supply Chest</t>
+          <t>Rương Vật Tư Cơ Bản</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27945,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Giai đoạn II</t>
+          <t>Giai Đoạn II</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28015,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Voidspawn: Iceglint Dancer</t>
+          <t>Voidspawn: Vũ Công Băng Giá</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28085,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>"Unnamed Entity"</t>
+          <t>"Thực Thể Vô Danh"</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28155,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Monster Spawner</t>
+          <t>Bộ tạo quái vật</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28225,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Book Namipon Shuttle</t>
+          <t>Tàu Con Thoi Namipon Sách</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28365,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>KU-Cage</t>
+          <t>KU-Lồng</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28505,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Lấy sữa</t>
+          <t>Lấy sữa đi</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28715,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Nhà nghiên cứu hào hứng</t>
+          <t>Nhà nghiên cứu hứng thú</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28785,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Violet Coral</t>
+          <t>San Hô Tím</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28855,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Flying Bird</t>
+          <t>Chim bay</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -29065,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Acceleration Ring</t>
+          <t>Nhẫn Tăng Tốc</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29135,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29415,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Drone Grapple</t>
+          <t>Móc Drone</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29485,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>: Duskfall's Blaze</t>
+          <t>: Ánh Lửa Hoàng Hôn</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29625,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Sitting Doll</t>
+          <t>Búp Bê Ngồi</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29695,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Nền Levitation trống</t>
+          <t>Nền bay trống</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29765,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Ký ức Ác mộng</t>
+          <t>Ký Ức Ác Mộng</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29835,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Slightly Aged Diary</t>
+          <t>Nhật Ký Đã Ố vàng Một Chút</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29905,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Xem trang nhật ký bí ẩn</t>
+          <t>Xem trang nhật ký bí ẩn.</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -30115,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Teensy Weensy</t>
+          <t>Nhóc Tí Hon</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30395,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Mở hộp quà</t>
+          <t>Mở hộp quà nào</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30465,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Sworddance Stance</t>
+          <t>Tư Thế Vũ Kiếm</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30675,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Carlotta Cube</t>
+          <t>Khối Carlotta</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30885,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Ouming</t>
+          <t>Ừm ừm...</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30955,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Sigrika Dorm Door Status Log</t>
+          <t>Nhật ký trạng thái cửa ký túc xá Sigrika</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31025,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Tiến tới nửa sau</t>
+          <t>Bước vào hiệp hai</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31235,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Initiate</t>
+          <t>Bắt đầu</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31305,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>test/</t>
+          <t>Thử nghiệm/</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31585,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Blood Weep: Rebel</t>
+          <t>Máu Rơi: Kẻ Nổi Loạn</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31655,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Lustrous Trophy Chest</t>
+          <t>Rương Kho Báu Luster</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31795,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Nhà Nghiên Cứu Cẩn Thận</t>
+          <t>Nhà Nghiên Cứu Tỉ Mỉ</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -32005,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Outgoing Fan</t>
+          <t>Người Hâm Mộ Ngoại Tuyến</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32145,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Những Mảnh Ghép Suy Tư Lặng Lẽ</t>
+          <t>Những Mảnh Suy Tư Lặng Lẽ</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32285,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Sư Tử Bóng Đá Vinh Quang</t>
+          <t>Sư Tử Vinh Quang - Giai Đoạn Truy Cập Sớm</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32495,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Bay theo nhịp điệu</t>
+          <t>Bay theo Nhịp Điệu</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32635,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>placeholder</t>
+          <t>vị trí tạm</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32775,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Luanquan</t>
+          <t>Loan Tuyền</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32985,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Main Core</t>
+          <t>Lõi Chính</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33055,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Question</t>
+          <t>Câu hỏi</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33125,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Enter</t>
+          <t>Vào</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33195,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Dream Pliferer</t>
+          <t>Kẻ Trộm Giấc Mơ</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33265,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Confere</t>
+          <t>Hội nghị</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33335,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Blubbin Puffin</t>
+          <t>Chim Cúc Cu Sủi Bọt</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33685,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Luo muốn chào bạn</t>
+          <t>Luo muốn chào cậu</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33895,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Thám hiểm sâu trong kho tàng</t>
+          <t>Đi sâu vào lòng kho tàng</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -34245,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Shengmao</t>
+          <t>Thăng Mao</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34385,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Advanced Trophy Chest</t>
+          <t>Rương Chiến Lợi Phẩm Cao Cấp</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34525,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Nhận phòng tại Khách sạn Leonidas</t>
+          <t>Nhận phòng tại khách sạn Leonidas</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34595,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Purify</t>
+          <t>Tinh Luyện</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34665,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34735,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Hiyuki's White Bird</t>
+          <t>Chim Trắng của Hiyuki</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34805,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Bridged Dreamscape</t>
+          <t>Giấc Mộng Kết Nối</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34875,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Additional Rule Text</t>
+          <t>Nội dung Quy tắc bổ sung</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34945,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Yongxin</t>
+          <t>Dũng Tâm</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35015,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Test</t>
+          <t>Kiểm tra</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35085,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>"Swim, Gulpuff, Swim" Device</t>
+          <t>"Thiết Bị 'Bơi Đi, Gulpuff, Bơi'"</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35155,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Jianghui</t>
+          <t>Khương Huy</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35225,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Chiếc Ghế Dành Cho Kẻ Quyền Uy</t>
+          <t>Ghế của Kẻ Quyền Uy</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35295,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>KU-Roro the Pot</t>
+          <t>Juebi Village</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35435,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Nervous Acolyte</t>
+          <t>Tín Đồ Lo Lắng</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
